--- a/traveldiary/data/TravelDiary_Info.xlsx
+++ b/traveldiary/data/TravelDiary_Info.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rnli-my.sharepoint.com/personal/richard_martin3_rnli_org_uk/Documents/02_Personal Projects/01_Travel/Final_2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a5878aca83ffe84e/Documents/1_Personal/05_Travel/03_Mapping/01_Travel/TravelDiary/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="940" documentId="8_{B0177ED4-AC48-4570-B34C-50BA25418F2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20F2E868-6028-4F28-8DD0-14B93FFD23A7}"/>
+  <xr:revisionPtr revIDLastSave="941" documentId="8_{B0177ED4-AC48-4570-B34C-50BA25418F2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{35D3E552-B523-4E53-BA84-4A1B4A5507CB}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7C2DBC9F-F133-4F31-9DC3-6D8A2F6D5AB8}"/>
+    <workbookView xWindow="2892" yWindow="2892" windowWidth="17280" windowHeight="9960" activeTab="3" xr2:uid="{7C2DBC9F-F133-4F31-9DC3-6D8A2F6D5AB8}"/>
   </bookViews>
   <sheets>
     <sheet name="To Do" sheetId="4" r:id="rId1"/>
@@ -649,9 +649,6 @@
     <t>Uni field trip.  Cliffs of Moher - lot of drinking!</t>
   </si>
   <si>
-    <t>2002 (Uni), 2009 (Uni lads), 2015 (Norther Ireland),  2019 (Dingle)</t>
-  </si>
-  <si>
     <t>Amsterdam</t>
   </si>
   <si>
@@ -752,6 +749,9 @@
   </si>
   <si>
     <t>Use Cursor to update current template - use map libre - nice icons though/ folium sty;e</t>
+  </si>
+  <si>
+    <t>2002 (Uni), 2009 (Uni lads), 2015 (Northern Ireland),  2019 (Dingle)</t>
   </si>
 </sst>
 </file>
@@ -1642,46 +1642,46 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B9" t="s">
         <v>221</v>
-      </c>
-      <c r="B9" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -1689,20 +1689,20 @@
         <v>129</v>
       </c>
       <c r="B11" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B13" t="s">
         <v>223</v>
-      </c>
-      <c r="B13" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
@@ -1730,7 +1730,7 @@
   <sheetData>
     <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>82</v>
@@ -1754,12 +1754,12 @@
         <v>84</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>102</v>
@@ -1788,7 +1788,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>102</v>
@@ -1812,12 +1812,12 @@
         <v>30</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>102</v>
@@ -1846,7 +1846,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>102</v>
@@ -1875,7 +1875,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>120</v>
@@ -1904,7 +1904,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>102</v>
@@ -1928,12 +1928,12 @@
         <v>30</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>102</v>
@@ -1962,7 +1962,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>102</v>
@@ -1986,12 +1986,12 @@
         <v>15</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>102</v>
@@ -2020,7 +2020,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>102</v>
@@ -2049,7 +2049,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>102</v>
@@ -2078,7 +2078,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>102</v>
@@ -2107,7 +2107,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>102</v>
@@ -2136,7 +2136,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>102</v>
@@ -2165,7 +2165,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>102</v>
@@ -2194,7 +2194,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>120</v>
@@ -2223,7 +2223,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>124</v>
@@ -2252,7 +2252,7 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>120</v>
@@ -2276,12 +2276,12 @@
         <v>172</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>106</v>
@@ -2310,7 +2310,7 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>102</v>
@@ -2339,7 +2339,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>102</v>
@@ -2368,7 +2368,7 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>106</v>
@@ -2397,7 +2397,7 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>106</v>
@@ -2426,7 +2426,7 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>104</v>
@@ -2450,12 +2450,12 @@
         <v>172</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>106</v>
@@ -2484,7 +2484,7 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>102</v>
@@ -2513,7 +2513,7 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>106</v>
@@ -2542,7 +2542,7 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>102</v>
@@ -2571,7 +2571,7 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>102</v>
@@ -2600,7 +2600,7 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>106</v>
@@ -2629,7 +2629,7 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>106</v>
@@ -2658,7 +2658,7 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>132</v>
@@ -2687,7 +2687,7 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>104</v>
@@ -2716,7 +2716,7 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>102</v>
@@ -2745,7 +2745,7 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>106</v>
@@ -2774,7 +2774,7 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>106</v>
@@ -2803,7 +2803,7 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>106</v>
@@ -2832,7 +2832,7 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>106</v>
@@ -2861,7 +2861,7 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>102</v>
@@ -2890,7 +2890,7 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>102</v>
@@ -2919,7 +2919,7 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>102</v>
@@ -2948,7 +2948,7 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>102</v>
@@ -2977,7 +2977,7 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>102</v>
@@ -3001,12 +3001,12 @@
         <v>172</v>
       </c>
       <c r="I44" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>102</v>
@@ -3035,7 +3035,7 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>106</v>
@@ -3064,7 +3064,7 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>102</v>
@@ -3093,7 +3093,7 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>104</v>
@@ -3122,7 +3122,7 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>106</v>
@@ -3151,7 +3151,7 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>106</v>
@@ -3180,7 +3180,7 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>106</v>
@@ -3209,7 +3209,7 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>102</v>
@@ -3238,7 +3238,7 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>102</v>
@@ -3247,7 +3247,7 @@
         <v>14</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E53" s="5">
         <v>2019</v>
@@ -3262,12 +3262,12 @@
         <v>172</v>
       </c>
       <c r="I53" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>102</v>
@@ -3296,7 +3296,7 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>102</v>
@@ -3325,7 +3325,7 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>132</v>
@@ -3354,7 +3354,7 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>106</v>
@@ -3383,7 +3383,7 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>102</v>
@@ -3412,7 +3412,7 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>102</v>
@@ -3441,7 +3441,7 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>102</v>
@@ -3470,7 +3470,7 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>102</v>
@@ -3494,12 +3494,12 @@
         <v>15</v>
       </c>
       <c r="I61" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>104</v>
@@ -3528,7 +3528,7 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>106</v>
@@ -3557,7 +3557,7 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>106</v>
@@ -3586,7 +3586,7 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>120</v>
@@ -3615,7 +3615,7 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>102</v>
@@ -3624,7 +3624,7 @@
         <v>116</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E66" s="5">
         <v>2025</v>
@@ -3639,12 +3639,12 @@
         <v>172</v>
       </c>
       <c r="I66" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>102</v>
@@ -3673,16 +3673,16 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>102</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E68" s="5">
         <v>2026</v>
@@ -3694,10 +3694,10 @@
         <v>11</v>
       </c>
       <c r="H68" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I68" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
   </sheetData>
@@ -4330,7 +4330,7 @@
         <v>200</v>
       </c>
       <c r="E39" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
@@ -4344,7 +4344,7 @@
         <v>4</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>207</v>
+        <v>241</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
@@ -4352,7 +4352,7 @@
         <v>102</v>
       </c>
       <c r="B41" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C41">
         <v>1</v>

--- a/traveldiary/data/TravelDiary_Info.xlsx
+++ b/traveldiary/data/TravelDiary_Info.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a5878aca83ffe84e/Documents/1_Personal/05_Travel/03_Mapping/01_Travel/TravelDiary/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="941" documentId="8_{B0177ED4-AC48-4570-B34C-50BA25418F2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{35D3E552-B523-4E53-BA84-4A1B4A5507CB}"/>
+  <xr:revisionPtr revIDLastSave="973" documentId="8_{B0177ED4-AC48-4570-B34C-50BA25418F2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6E65BE1-26F4-4EB2-AC87-C658F816FA9A}"/>
   <bookViews>
-    <workbookView xWindow="2892" yWindow="2892" windowWidth="17280" windowHeight="9960" activeTab="3" xr2:uid="{7C2DBC9F-F133-4F31-9DC3-6D8A2F6D5AB8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{7C2DBC9F-F133-4F31-9DC3-6D8A2F6D5AB8}"/>
   </bookViews>
   <sheets>
     <sheet name="To Do" sheetId="4" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="249">
   <si>
     <t>Country</t>
   </si>
@@ -752,6 +752,27 @@
   </si>
   <si>
     <t>2002 (Uni), 2009 (Uni lads), 2015 (Northern Ireland),  2019 (Dingle)</t>
+  </si>
+  <si>
+    <t>Venezuela</t>
+  </si>
+  <si>
+    <t>Caracas</t>
+  </si>
+  <si>
+    <t>2 x 7.2/7.5mag earthquakes.  Camp visit was life changing experience in seeing the solar panel generators and spirit of locals.  Venezuela = green!!</t>
+  </si>
+  <si>
+    <t>Colombia</t>
+  </si>
+  <si>
+    <t>Bogota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flying visit - 11hr stop over in city - saw key sites.  Lovely views over city and amazing street art everywhere </t>
+  </si>
+  <si>
+    <t>Have to rename the geojson file to json in order for it to work</t>
   </si>
 </sst>
 </file>
@@ -1247,7 +1268,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
@@ -1259,6 +1280,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1315,6 +1337,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1707,6 +1733,9 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
+      <c r="B16" s="7" t="s">
+        <v>248</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1715,7 +1744,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B572C6AD-5AF1-44F7-8A58-B3CB27EB5C49}">
-  <dimension ref="A1:I68"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
@@ -3698,6 +3727,64 @@
       </c>
       <c r="I68" s="5" t="s">
         <v>228</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>231</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="D69" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="E69" s="5">
+        <v>2026</v>
+      </c>
+      <c r="F69" s="5">
+        <v>0</v>
+      </c>
+      <c r="G69" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="H69" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I69" s="5" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>231</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="D70" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="E70" s="5">
+        <v>2026</v>
+      </c>
+      <c r="F70" s="5">
+        <v>8</v>
+      </c>
+      <c r="G70" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H70" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I70" s="5" t="s">
+        <v>247</v>
       </c>
     </row>
   </sheetData>
@@ -3764,7 +3851,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2C48894-26D5-4F1D-86E5-7EFCA631889F}">
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.109375" bestFit="1" customWidth="1"/>
@@ -4361,6 +4448,34 @@
         <v>2026</v>
       </c>
     </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>124</v>
+      </c>
+      <c r="B42" t="s">
+        <v>242</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+      <c r="D42" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>124</v>
+      </c>
+      <c r="B43" t="s">
+        <v>245</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+      <c r="D43" s="4">
+        <v>2026</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/traveldiary/data/TravelDiary_Info.xlsx
+++ b/traveldiary/data/TravelDiary_Info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a5878aca83ffe84e/Documents/1_Personal/05_Travel/03_Mapping/01_Travel/TravelDiary/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="973" documentId="8_{B0177ED4-AC48-4570-B34C-50BA25418F2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6E65BE1-26F4-4EB2-AC87-C658F816FA9A}"/>
+  <xr:revisionPtr revIDLastSave="985" documentId="8_{B0177ED4-AC48-4570-B34C-50BA25418F2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1DF462A5-E1F7-4778-9292-E16CFA6637EF}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{7C2DBC9F-F133-4F31-9DC3-6D8A2F6D5AB8}"/>
   </bookViews>
@@ -325,9 +325,6 @@
     <t>Fuerventura</t>
   </si>
   <si>
-    <t>Long beach walks, lazy trip away in sunshine, mountain walk and catamaran</t>
-  </si>
-  <si>
     <t>Total Visits</t>
   </si>
   <si>
@@ -773,6 +770,9 @@
   </si>
   <si>
     <t>Have to rename the geojson file to json in order for it to work</t>
+  </si>
+  <si>
+    <t>Cool lighthouse, lovely long beaches/bars. fantastic walk up mountain with views, amazing catamaran trip</t>
   </si>
 </sst>
 </file>
@@ -915,7 +915,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1107,6 +1107,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -1268,7 +1274,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
@@ -1281,6 +1287,7 @@
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1668,73 +1675,73 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B9" t="s">
         <v>220</v>
-      </c>
-      <c r="B9" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B11" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B13" t="s">
         <v>222</v>
-      </c>
-      <c r="B13" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
   </sheetData>
@@ -1759,7 +1766,7 @@
   <sheetData>
     <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>82</v>
@@ -1783,15 +1790,15 @@
         <v>84</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>45</v>
@@ -1812,15 +1819,15 @@
         <v>30</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>4</v>
@@ -1841,15 +1848,15 @@
         <v>30</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>7</v>
@@ -1875,16 +1882,16 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E5" s="5">
         <v>1994</v>
@@ -1899,21 +1906,21 @@
         <v>30</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E6" s="5">
         <v>1996</v>
@@ -1928,15 +1935,15 @@
         <v>30</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>12</v>
@@ -1957,15 +1964,15 @@
         <v>30</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>79</v>
@@ -1983,24 +1990,24 @@
         <v>6</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E9" s="5">
         <v>2001</v>
@@ -2009,27 +2016,27 @@
         <v>7</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>15</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>81</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E10" s="5">
         <v>2002</v>
@@ -2044,15 +2051,15 @@
         <v>30</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>16</v>
@@ -2067,21 +2074,21 @@
         <v>7</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>15</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>7</v>
@@ -2102,15 +2109,15 @@
         <v>30</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>12</v>
@@ -2136,16 +2143,16 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>196</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>197</v>
       </c>
       <c r="E14" s="2">
         <v>2006</v>
@@ -2154,21 +2161,21 @@
         <v>0</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>7</v>
@@ -2183,21 +2190,21 @@
         <v>7</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>15</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>14</v>
@@ -2212,27 +2219,27 @@
         <v>7</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H16" s="5" t="s">
         <v>15</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>28</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E17" s="5">
         <v>2009</v>
@@ -2241,7 +2248,7 @@
         <v>8</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H17" s="5" t="s">
         <v>30</v>
@@ -2252,10 +2259,10 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>31</v>
@@ -2270,21 +2277,21 @@
         <v>8</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>10</v>
@@ -2302,24 +2309,24 @@
         <v>19</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>23</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E20" s="5">
         <v>2009</v>
@@ -2331,24 +2338,24 @@
         <v>19</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>81</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E21" s="5">
         <v>2009</v>
@@ -2363,15 +2370,15 @@
         <v>30</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>7</v>
@@ -2386,27 +2393,27 @@
         <v>7</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H22" s="5" t="s">
         <v>15</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>23</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E23" s="5">
         <v>2010</v>
@@ -2421,15 +2428,15 @@
         <v>24</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>34</v>
@@ -2450,21 +2457,21 @@
         <v>30</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>36</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E25" s="5">
         <v>2011</v>
@@ -2476,18 +2483,18 @@
         <v>11</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>34</v>
@@ -2508,15 +2515,15 @@
         <v>30</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>38</v>
@@ -2537,21 +2544,21 @@
         <v>15</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>43</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E28" s="5">
         <v>2012</v>
@@ -2560,21 +2567,21 @@
         <v>7</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H28" s="5" t="s">
         <v>30</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>40</v>
@@ -2595,21 +2602,21 @@
         <v>30</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>42</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E30" s="5">
         <v>2012</v>
@@ -2624,21 +2631,21 @@
         <v>30</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E31" s="5">
         <v>2013</v>
@@ -2647,21 +2654,21 @@
         <v>9</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H31" s="5" t="s">
         <v>30</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>47</v>
@@ -2676,27 +2683,27 @@
         <v>8</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>49</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E33" s="5">
         <v>2013</v>
@@ -2711,21 +2718,21 @@
         <v>15</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>36</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E34" s="5">
         <v>2013</v>
@@ -2745,10 +2752,10 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>45</v>
@@ -2763,21 +2770,21 @@
         <v>7.5</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H35" s="5" t="s">
         <v>15</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>50</v>
@@ -2798,15 +2805,15 @@
         <v>30</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>52</v>
@@ -2827,15 +2834,15 @@
         <v>15</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>54</v>
@@ -2850,21 +2857,21 @@
         <v>8</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H38" s="5" t="s">
         <v>30</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>54</v>
@@ -2882,24 +2889,24 @@
         <v>19</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I39" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E40" s="5">
         <v>2015</v>
@@ -2911,24 +2918,24 @@
         <v>11</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I40" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>81</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E41" s="5">
         <v>2015</v>
@@ -2943,15 +2950,15 @@
         <v>30</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>59</v>
@@ -2972,15 +2979,15 @@
         <v>30</v>
       </c>
       <c r="I42" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>57</v>
@@ -3001,15 +3008,15 @@
         <v>30</v>
       </c>
       <c r="I43" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>62</v>
@@ -3024,21 +3031,21 @@
         <v>8.5</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I44" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>59</v>
@@ -3059,21 +3066,21 @@
         <v>30</v>
       </c>
       <c r="I45" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C46" s="5" t="s">
         <v>50</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E46" s="5">
         <v>2018</v>
@@ -3088,21 +3095,21 @@
         <v>30</v>
       </c>
       <c r="I46" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>78</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E47" s="5">
         <v>2018</v>
@@ -3114,24 +3121,24 @@
         <v>64</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I47" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E48" s="5">
         <v>2019</v>
@@ -3146,21 +3153,21 @@
         <v>30</v>
       </c>
       <c r="I48" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>66</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E49" s="5">
         <v>2019</v>
@@ -3180,10 +3187,10 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C50" s="5" t="s">
         <v>52</v>
@@ -3209,10 +3216,10 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>68</v>
@@ -3238,16 +3245,16 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>81</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E52" s="5">
         <v>2019</v>
@@ -3262,21 +3269,21 @@
         <v>15</v>
       </c>
       <c r="I52" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E53" s="5">
         <v>2019</v>
@@ -3285,21 +3292,21 @@
         <v>8</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I53" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>38</v>
@@ -3325,16 +3332,16 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C55" s="5" t="s">
         <v>69</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E55" s="5">
         <v>2022</v>
@@ -3354,10 +3361,10 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>49</v>
@@ -3383,10 +3390,10 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C57" s="5" t="s">
         <v>68</v>
@@ -3412,10 +3419,10 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C58" s="5" t="s">
         <v>70</v>
@@ -3436,21 +3443,21 @@
         <v>30</v>
       </c>
       <c r="I58" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C59" s="5" t="s">
         <v>72</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E59" s="5">
         <v>2023</v>
@@ -3459,7 +3466,7 @@
         <v>8</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H59" s="5" t="s">
         <v>30</v>
@@ -3469,11 +3476,11 @@
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>231</v>
+      <c r="A60" s="8" t="s">
+        <v>230</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C60" s="5" t="s">
         <v>94</v>
@@ -3498,17 +3505,17 @@
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>231</v>
+      <c r="A61" s="8" t="s">
+        <v>230</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C61" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E61" s="5">
         <v>2024</v>
@@ -3523,21 +3530,21 @@
         <v>15</v>
       </c>
       <c r="I61" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>231</v>
+      <c r="A62" s="8" t="s">
+        <v>230</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C62" s="5" t="s">
         <v>74</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E62" s="5">
         <v>2025</v>
@@ -3546,7 +3553,7 @@
         <v>8</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H62" s="5" t="s">
         <v>30</v>
@@ -3556,11 +3563,11 @@
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>231</v>
+      <c r="A63" s="8" t="s">
+        <v>230</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C63" s="5" t="s">
         <v>54</v>
@@ -3581,21 +3588,21 @@
         <v>30</v>
       </c>
       <c r="I63" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
-        <v>231</v>
+      <c r="A64" s="8" t="s">
+        <v>230</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C64" s="5" t="s">
         <v>75</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E64" s="5">
         <v>2025</v>
@@ -3610,21 +3617,21 @@
         <v>30</v>
       </c>
       <c r="I64" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
-        <v>231</v>
+      <c r="A65" s="8" t="s">
+        <v>230</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C65" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E65" s="5">
         <v>2025</v>
@@ -3643,17 +3650,17 @@
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
-        <v>231</v>
+      <c r="A66" s="8" t="s">
+        <v>230</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E66" s="5">
         <v>2025</v>
@@ -3665,24 +3672,24 @@
         <v>19</v>
       </c>
       <c r="H66" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I66" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
-        <v>231</v>
+      <c r="A67" s="8" t="s">
+        <v>230</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C67" s="5" t="s">
         <v>98</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E67" s="5">
         <v>2026</v>
@@ -3691,27 +3698,27 @@
         <v>8.5</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H67" s="5" t="s">
         <v>30</v>
       </c>
       <c r="I67" s="5" t="s">
-        <v>99</v>
+        <v>248</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
-        <v>231</v>
+      <c r="A68" s="8" t="s">
+        <v>230</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E68" s="5">
         <v>2026</v>
@@ -3723,24 +3730,24 @@
         <v>11</v>
       </c>
       <c r="H68" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I68" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
-        <v>231</v>
+      <c r="A69" s="8" t="s">
+        <v>230</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C69" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="D69" s="5" t="s">
         <v>242</v>
-      </c>
-      <c r="D69" s="5" t="s">
-        <v>243</v>
       </c>
       <c r="E69" s="5">
         <v>2026</v>
@@ -3755,21 +3762,21 @@
         <v>30</v>
       </c>
       <c r="I69" s="5" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A70" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C70" s="5" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
-        <v>231</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="C70" s="5" t="s">
+      <c r="D70" s="5" t="s">
         <v>245</v>
-      </c>
-      <c r="D70" s="5" t="s">
-        <v>246</v>
       </c>
       <c r="E70" s="5">
         <v>2026</v>
@@ -3784,7 +3791,7 @@
         <v>30</v>
       </c>
       <c r="I70" s="5" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
   </sheetData>
@@ -3817,7 +3824,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -3825,7 +3832,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -3833,7 +3840,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -3841,7 +3848,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -3869,10 +3876,10 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>101</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>91</v>
@@ -3880,7 +3887,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -3889,15 +3896,15 @@
         <v>3</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B3" t="s">
         <v>72</v>
@@ -3911,7 +3918,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B4" t="s">
         <v>74</v>
@@ -3925,7 +3932,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B5" t="s">
         <v>65</v>
@@ -3939,7 +3946,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B6" t="s">
         <v>36</v>
@@ -3948,12 +3955,12 @@
         <v>2</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B7" t="s">
         <v>66</v>
@@ -3967,7 +3974,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B8" t="s">
         <v>34</v>
@@ -3976,12 +3983,12 @@
         <v>2</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B9" t="s">
         <v>50</v>
@@ -3990,12 +3997,12 @@
         <v>2</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B10" t="s">
         <v>52</v>
@@ -4004,12 +4011,12 @@
         <v>2</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B11" t="s">
         <v>44</v>
@@ -4023,7 +4030,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B12" t="s">
         <v>75</v>
@@ -4037,7 +4044,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B13" t="s">
         <v>47</v>
@@ -4051,7 +4058,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B14" t="s">
         <v>23</v>
@@ -4060,12 +4067,12 @@
         <v>2</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B15" t="s">
         <v>68</v>
@@ -4074,12 +4081,12 @@
         <v>2</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B16" t="s">
         <v>43</v>
@@ -4093,7 +4100,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B17" t="s">
         <v>54</v>
@@ -4102,12 +4109,12 @@
         <v>3</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B18" t="s">
         <v>70</v>
@@ -4121,7 +4128,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B19" t="s">
         <v>76</v>
@@ -4135,7 +4142,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B20" t="s">
         <v>28</v>
@@ -4149,7 +4156,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B21" t="s">
         <v>57</v>
@@ -4163,7 +4170,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B22" t="s">
         <v>59</v>
@@ -4172,12 +4179,12 @@
         <v>2</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B23" t="s">
         <v>45</v>
@@ -4186,15 +4193,15 @@
         <v>2</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B24" t="s">
         <v>38</v>
@@ -4203,12 +4210,12 @@
         <v>2</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B25" t="s">
         <v>69</v>
@@ -4222,7 +4229,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B26" t="s">
         <v>14</v>
@@ -4231,12 +4238,12 @@
         <v>3</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B27" t="s">
         <v>16</v>
@@ -4245,12 +4252,12 @@
         <v>1</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B28" t="s">
         <v>42</v>
@@ -4264,7 +4271,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B29" t="s">
         <v>62</v>
@@ -4278,7 +4285,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B30" t="s">
         <v>4</v>
@@ -4287,15 +4294,15 @@
         <v>2</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B31" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -4306,7 +4313,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B32" t="s">
         <v>78</v>
@@ -4321,7 +4328,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B33" t="s">
         <v>7</v>
@@ -4330,12 +4337,12 @@
         <v>4</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B34" t="s">
         <v>40</v>
@@ -4344,12 +4351,12 @@
         <v>2</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B35" t="s">
         <v>79</v>
@@ -4363,7 +4370,7 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B36" t="s">
         <v>10</v>
@@ -4372,12 +4379,12 @@
         <v>2</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B37" t="s">
         <v>49</v>
@@ -4386,12 +4393,12 @@
         <v>2</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B38" t="s">
         <v>31</v>
@@ -4405,24 +4412,24 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B39" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C39">
         <v>3</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E39" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B40" t="s">
         <v>81</v>
@@ -4431,15 +4438,15 @@
         <v>4</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B41" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C41">
         <v>1</v>
@@ -4450,10 +4457,10 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B42" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C42">
         <v>1</v>
@@ -4464,10 +4471,10 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B43" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C43">
         <v>1</v>
